--- a/Objetivos.xlsx
+++ b/Objetivos.xlsx
@@ -1,36 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objetivos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pontuacao" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Objetivos" sheetId="1" r:id="rId1"/>
+    <sheet name="Pontuacao" sheetId="2" r:id="rId2"/>
+    <sheet name="Historico" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,80 +67,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -201,6 +152,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -235,6 +187,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -269,20 +222,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -404,149 +353,636 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I16"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Tarefa</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Concluída</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Prazo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Prioridade</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Criado em</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Concluído em</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Não cumprido</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Penalizado automaticamente</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Categoria</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Tarefa</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Concluída</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Prazo</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Prioridade</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Criado em</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Concluído em</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Não cumprido</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Penalizado automaticamente</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Ir pegar o protetor de suspenção</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>Tempo livre</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-07-11T04:48:29.901Z</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Pegar CNH</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Se programe</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sondar Pichau e Terabyte, Sondar Senai</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Tentar doar os gatos</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Resolver coisas para o tio aqui na Cida (mesa de bilhar e outra coisa que esqueci)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Delegue</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ir terminar de arrumar minha ex-casa (organizar, limpar, ver os gatos)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Objetivos Gerais</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Decidir se fico em Joinville ou Blumenau</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-07-11T04:48:51.614Z</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Objetivos Gerais</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Começar engenharia de Software</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Objetivos Gerais</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Arrumar um bom novo emprego</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Objetivos Gerais</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Juntar dinheiro (pelo menos o valor da rescisão)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>Se programe</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Objetivos Gerais</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Comprar carro ou moto</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>Delegue</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Objetivos a Médio e Longo Prazo</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Fazer faculdade?</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>Se programe</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Objetivos a Médio e Longo Prazo</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sondar opções de carros e motos</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>Tempo livre</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Objetivos a Médio e Longo Prazo</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sondar casas em Joinville ou Blumenau</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>Tempo livre</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Joinville ou Blumenau?</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-07-12</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-07-11T04:48:40.902Z</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Não</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Saldo Atual</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Saldo Inicial</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Saldo Atual</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Saldo Inicial</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
+        <v>1210</v>
+      </c>
+      <c r="B2">
         <v>1000</v>
       </c>
-      <c r="B2" t="n">
-        <v>1000</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Variação</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Saldo após</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Data</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Variação</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Motivo</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Saldo após</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-07-11T04:48:29.901Z</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Concluído: Ir pegar o protetor de suspenção</v>
+      </c>
+      <c r="D2">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-07-11T04:48:40.902Z</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Concluído: Joinville ou Blumenau?</v>
+      </c>
+      <c r="D3">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-07-11T04:48:51.614Z</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Concluído: Decidir se fico em Joinville ou Blumenau</v>
+      </c>
+      <c r="D4">
+        <v>1210</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Objetivos.xlsx
+++ b/Objetivos.xlsx
@@ -539,7 +539,7 @@
         <v>Não</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-17</v>
       </c>
       <c r="E5" t="str">
         <v>Urgente</v>
@@ -594,10 +594,10 @@
         <v>Ir terminar de arrumar minha ex-casa (organizar, limpar, ver os gatos)</v>
       </c>
       <c r="C7" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-17</v>
       </c>
       <c r="E7" t="str">
         <v>Urgente</v>
@@ -606,7 +606,7 @@
         <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2026-07-15T21:17:04.461Z</v>
       </c>
       <c r="H7" t="str">
         <v>Não</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1210</v>
+        <v>1310</v>
       </c>
       <c r="B2">
         <v>1000</v>
@@ -916,7 +916,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D9"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -980,9 +980,79 @@
         <v>1210</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-07-15T21:16:17.841Z</v>
+      </c>
+      <c r="B5">
+        <v>-100</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Prazo vencido: Tentar doar os gatos</v>
+      </c>
+      <c r="D5">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-07-15T21:16:17.841Z</v>
+      </c>
+      <c r="B6">
+        <v>-100</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Prazo vencido: Ir terminar de arrumar minha ex-casa (organizar, limpar, ver os gatos)</v>
+      </c>
+      <c r="D6">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-07-15T21:16:39.576Z</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Penalidade de prazo revertida: Ir terminar de arrumar minha ex-casa (organizar, limpar, ver os gatos)</v>
+      </c>
+      <c r="D7">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-07-15T21:16:48.317Z</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Penalidade de prazo revertida: Tentar doar os gatos</v>
+      </c>
+      <c r="D8">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-07-15T21:17:04.461Z</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Concluído: Ir terminar de arrumar minha ex-casa (organizar, limpar, ver os gatos)</v>
+      </c>
+      <c r="D9">
+        <v>1310</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Objetivos.xlsx
+++ b/Objetivos.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -876,9 +876,67 @@
         <v>Não</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Objetivos a Médio e Longo Prazo</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Viajar (Cruzeiro)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>Se programe</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-07-15T21:31:25.002Z</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Não</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Objetivos Próximos</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Entrevista TLP</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>Se programe</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-07-15T21:32:16.377Z</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Não</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Objetivos.xlsx
+++ b/Objetivos.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -934,9 +934,38 @@
         <v>Não</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Objetivos Gerais</v>
+      </c>
+      <c r="B19" t="str">
+        <v>esbarrar com um amor? (estar aberto para)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v>Urgente</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-07-15T21:42:11.308Z</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>Não</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Não</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Objetivos.xlsx
+++ b/Objetivos.xlsx
@@ -399,17 +399,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="50.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,24 +421,27 @@
         <v>Tarefa</v>
       </c>
       <c r="C1" t="str">
+        <v>Descrição</v>
+      </c>
+      <c r="D1" t="str">
         <v>Concluída</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Prazo</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Prioridade</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Criado em</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Concluído em</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Não cumprido</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Penalizado automaticamente</v>
       </c>
     </row>
@@ -449,24 +453,27 @@
         <v>Ir pegar o protetor de suspenção</v>
       </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
         <v>Sim</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>Tempo livre</v>
       </c>
-      <c r="F2" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G2" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="H2" t="str">
         <v>2026-07-11T04:48:29.901Z</v>
       </c>
-      <c r="H2" t="str">
-        <v>Não</v>
-      </c>
       <c r="I2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -478,24 +485,27 @@
         <v>Pegar CNH</v>
       </c>
       <c r="C3" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="E3" t="str">
         <v>2026-07-17</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Se programe</v>
       </c>
-      <c r="F3" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H3" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -504,27 +514,30 @@
         <v>Objetivos Próximos</v>
       </c>
       <c r="B4" t="str">
-        <v>Sondar Pichau e Terabyte, Sondar Senai</v>
+        <v>Sondar</v>
       </c>
       <c r="C4" t="str">
-        <v>Não</v>
+        <v>Pichau, Terabyte e Senai</v>
       </c>
       <c r="D4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="E4" t="str">
         <v>2026-07-17</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F4" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G4" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H4" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -536,24 +549,27 @@
         <v>Tentar doar os gatos</v>
       </c>
       <c r="C5" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="E5" t="str">
         <v>2026-07-17</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F5" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H5" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -562,27 +578,30 @@
         <v>Objetivos Próximos</v>
       </c>
       <c r="B6" t="str">
-        <v>Resolver coisas para o tio aqui na Cida (mesa de bilhar e outra coisa que esqueci)</v>
+        <v>Resolver coisas Cida</v>
       </c>
       <c r="C6" t="str">
-        <v>Não</v>
+        <v>mesa de bilhar e outra coisa que esqueci</v>
       </c>
       <c r="D6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="E6" t="str">
         <v>2026-07-17</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>Delegue</v>
       </c>
-      <c r="F6" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G6" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H6" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J6" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -594,24 +613,27 @@
         <v>Ir terminar de arrumar minha ex-casa (organizar, limpar, ver os gatos)</v>
       </c>
       <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
         <v>Sim</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>2026-07-17</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F7" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G7" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="H7" t="str">
         <v>2026-07-15T21:17:04.461Z</v>
       </c>
-      <c r="H7" t="str">
-        <v>Não</v>
-      </c>
       <c r="I7" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J7" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -623,24 +645,27 @@
         <v>Decidir se fico em Joinville ou Blumenau</v>
       </c>
       <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
         <v>Sim</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F8" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G8" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="H8" t="str">
         <v>2026-07-11T04:48:51.614Z</v>
       </c>
-      <c r="H8" t="str">
-        <v>Não</v>
-      </c>
       <c r="I8" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J8" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -652,24 +677,27 @@
         <v>Começar engenharia de Software</v>
       </c>
       <c r="C9" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F9" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G9" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H9" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I9" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J9" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -681,24 +709,27 @@
         <v>Arrumar um bom novo emprego</v>
       </c>
       <c r="C10" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F10" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G10" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H10" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I10" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J10" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -707,27 +738,30 @@
         <v>Objetivos Gerais</v>
       </c>
       <c r="B11" t="str">
-        <v>Juntar dinheiro (pelo menos o valor da rescisão)</v>
+        <v>Juntar dinheiro</v>
       </c>
       <c r="C11" t="str">
-        <v>Não</v>
+        <v>pelo menos o valor da rescisão</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>Se programe</v>
       </c>
-      <c r="F11" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G11" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H11" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I11" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J11" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -739,24 +773,27 @@
         <v>Comprar carro ou moto</v>
       </c>
       <c r="C12" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>Delegue</v>
       </c>
-      <c r="F12" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G12" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H12" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I12" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J12" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -768,24 +805,27 @@
         <v>Fazer faculdade?</v>
       </c>
       <c r="C13" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>Se programe</v>
       </c>
-      <c r="F13" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G13" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H13" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I13" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J13" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -797,24 +837,27 @@
         <v>Sondar opções de carros e motos</v>
       </c>
       <c r="C14" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>Tempo livre</v>
       </c>
-      <c r="F14" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G14" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H14" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I14" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J14" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -823,27 +866,30 @@
         <v>Objetivos a Médio e Longo Prazo</v>
       </c>
       <c r="B15" t="str">
-        <v>Sondar casas em Joinville ou Blumenau</v>
+        <v>Sondar casas em Joinville</v>
       </c>
       <c r="C15" t="str">
-        <v>Não</v>
+        <v>Morar Sozinho?</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>Tempo livre</v>
       </c>
-      <c r="F15" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G15" t="str">
-        <v/>
+        <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H15" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I15" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J15" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -855,24 +901,27 @@
         <v>Joinville ou Blumenau?</v>
       </c>
       <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
         <v>Sim</v>
       </c>
-      <c r="D16" t="str">
+      <c r="E16" t="str">
         <v>2026-07-12</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F16" t="str">
-        <v>2026-07-11T04:37:04.779Z</v>
-      </c>
       <c r="G16" t="str">
+        <v>2026-07-11T04:37:04.779Z</v>
+      </c>
+      <c r="H16" t="str">
         <v>2026-07-11T04:48:40.902Z</v>
       </c>
-      <c r="H16" t="str">
-        <v>Não</v>
-      </c>
       <c r="I16" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J16" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -881,27 +930,30 @@
         <v>Objetivos a Médio e Longo Prazo</v>
       </c>
       <c r="B17" t="str">
-        <v>Viajar (Cruzeiro)</v>
+        <v>Viajar</v>
       </c>
       <c r="C17" t="str">
-        <v>Não</v>
+        <v>Cruzeiro, Maragogi, Pernambuco</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>Se programe</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>2026-07-15T21:31:25.002Z</v>
       </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
       <c r="H17" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I17" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J17" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -913,24 +965,27 @@
         <v>Entrevista TLP</v>
       </c>
       <c r="C18" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>Se programe</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>2026-07-15T21:32:16.377Z</v>
       </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
       <c r="H18" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I18" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J18" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -939,33 +994,36 @@
         <v>Objetivos Gerais</v>
       </c>
       <c r="B19" t="str">
-        <v>esbarrar com um amor? (estar aberto para)</v>
+        <v>esbarrar com um amor?</v>
       </c>
       <c r="C19" t="str">
-        <v>Não</v>
+        <v>estar aberto para isso</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>Não</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>Urgente</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>2026-07-15T21:42:11.308Z</v>
       </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
       <c r="H19" t="str">
-        <v>Não</v>
+        <v/>
       </c>
       <c r="I19" t="str">
+        <v>Não</v>
+      </c>
+      <c r="J19" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Objetivos.xlsx
+++ b/Objetivos.xlsx
@@ -520,7 +520,7 @@
         <v>Pichau, Terabyte e Senai</v>
       </c>
       <c r="D4" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="E4" t="str">
         <v>2026-07-17</v>
@@ -532,7 +532,7 @@
         <v>2026-07-11T04:37:04.779Z</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>2026-07-16T00:11:18.636Z</v>
       </c>
       <c r="I4" t="str">
         <v>Não</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1310</v>
+        <v>1410</v>
       </c>
       <c r="B2">
         <v>1000</v>
@@ -1061,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1195,9 +1195,23 @@
         <v>1310</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-07-16T00:11:18.636Z</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Concluído: Sondar</v>
+      </c>
+      <c r="D10">
+        <v>1410</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
   </ignoredErrors>
 </worksheet>
 </file>